--- a/BD_SEA.xlsx
+++ b/BD_SEA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcsfcomar.sharepoint.com/sites/grp_ces/Documentos compartidos/CicSFE_sp/Agro/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bcsfcomar.sharepoint.com/sites/grp_ces/Documentos compartidos/BD_sp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{23F28395-745B-4EA3-A92C-2120E6273E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F11C0F0D-D552-439D-986D-D44B6EC319D8}"/>
+  <xr:revisionPtr revIDLastSave="207" documentId="13_ncr:1_{23F28395-745B-4EA3-A92C-2120E6273E83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{38898794-FD60-48C3-9A42-E58A39041667}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Índice" sheetId="8" r:id="rId1"/>
@@ -293,7 +293,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1352" uniqueCount="407">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1359" uniqueCount="409">
   <si>
     <t>Título</t>
   </si>
@@ -1651,6 +1651,12 @@
       </rPr>
       <t xml:space="preserve">: superficie sembrada, superficie cosechada, rendimiento y producción del cultivo en el centro-norte de la provincia de Santa Fe </t>
     </r>
+  </si>
+  <si>
+    <t>2026/27</t>
+  </si>
+  <si>
+    <t>2026</t>
   </si>
 </sst>
 </file>
@@ -3576,13 +3582,13 @@
         <v>51</v>
       </c>
       <c r="E12" s="122" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F12" s="123" t="s">
         <v>47</v>
       </c>
       <c r="G12" s="124">
-        <v>45931</v>
+        <v>46308</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.2">
@@ -3748,7 +3754,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BG25"/>
+  <dimension ref="A1:BG26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="57" width="11.42578125" style="3"/>
@@ -7192,7 +7198,7 @@
         <v>5376015</v>
       </c>
       <c r="E24" s="23">
-        <v>33.086223343693263</v>
+        <v>33.086223343693298</v>
       </c>
       <c r="F24" s="33">
         <v>106300</v>
@@ -7372,178 +7378,357 @@
       <c r="A25" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="O25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="S25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="W25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="X25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AG25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AH25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AI25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AJ25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AK25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AL25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AM25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AO25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AR25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AS25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AT25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AX25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AY25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AZ25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="BA25" s="55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="BB25" s="59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="BC25" s="78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="BD25" s="68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="BE25" s="55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="BF25" s="73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="BG25" s="32" t="e">
+      <c r="B25" s="33">
+        <v>1665000</v>
+      </c>
+      <c r="C25" s="26">
+        <v>1660100</v>
+      </c>
+      <c r="D25" s="26">
+        <v>6090335</v>
+      </c>
+      <c r="E25" s="23">
+        <v>36.686555026805614</v>
+      </c>
+      <c r="F25" s="33">
+        <v>109300</v>
+      </c>
+      <c r="G25" s="26">
+        <v>104900</v>
+      </c>
+      <c r="H25" s="26">
+        <v>237940</v>
+      </c>
+      <c r="I25" s="23">
+        <v>22.7</v>
+      </c>
+      <c r="J25" s="33">
+        <v>30500</v>
+      </c>
+      <c r="K25" s="26">
+        <v>30500</v>
+      </c>
+      <c r="L25" s="26">
+        <v>81875</v>
+      </c>
+      <c r="M25" s="23">
+        <v>26.844262295081968</v>
+      </c>
+      <c r="N25" s="33">
+        <v>49800</v>
+      </c>
+      <c r="O25" s="26">
+        <v>49550</v>
+      </c>
+      <c r="P25" s="26">
+        <v>126645</v>
+      </c>
+      <c r="Q25" s="23">
+        <v>25.559031281533805</v>
+      </c>
+      <c r="R25" s="33">
+        <v>160000</v>
+      </c>
+      <c r="S25" s="26">
+        <v>159750</v>
+      </c>
+      <c r="T25" s="26">
+        <v>457085</v>
+      </c>
+      <c r="U25" s="23">
+        <v>28.612519561815336</v>
+      </c>
+      <c r="V25" s="33">
+        <v>151300</v>
+      </c>
+      <c r="W25" s="26">
+        <v>151300</v>
+      </c>
+      <c r="X25" s="26">
+        <v>438950</v>
+      </c>
+      <c r="Y25" s="23">
+        <v>29.011896893588897</v>
+      </c>
+      <c r="Z25" s="33">
+        <v>24600</v>
+      </c>
+      <c r="AA25" s="26">
+        <v>24600</v>
+      </c>
+      <c r="AB25" s="26">
+        <v>63110</v>
+      </c>
+      <c r="AC25" s="23">
+        <v>25.654471544715449</v>
+      </c>
+      <c r="AD25" s="33">
+        <v>1300</v>
+      </c>
+      <c r="AE25" s="26">
+        <v>1300</v>
+      </c>
+      <c r="AF25" s="26">
+        <v>3130</v>
+      </c>
+      <c r="AG25" s="23">
+        <v>24.076923076923077</v>
+      </c>
+      <c r="AH25" s="33">
+        <v>373200</v>
+      </c>
+      <c r="AI25" s="26">
+        <v>373200</v>
+      </c>
+      <c r="AJ25" s="26">
+        <v>1447300</v>
+      </c>
+      <c r="AK25" s="23">
+        <v>38.780814576634512</v>
+      </c>
+      <c r="AL25" s="33">
+        <v>157500</v>
+      </c>
+      <c r="AM25" s="26">
+        <v>157500</v>
+      </c>
+      <c r="AN25" s="26">
+        <v>579775</v>
+      </c>
+      <c r="AO25" s="23">
+        <v>36.81111111111111</v>
+      </c>
+      <c r="AP25" s="33">
+        <v>60000</v>
+      </c>
+      <c r="AQ25" s="26">
+        <v>60000</v>
+      </c>
+      <c r="AR25" s="26">
+        <v>213600</v>
+      </c>
+      <c r="AS25" s="23">
+        <v>35.6</v>
+      </c>
+      <c r="AT25" s="33">
+        <v>336500</v>
+      </c>
+      <c r="AU25" s="26">
+        <v>336500</v>
+      </c>
+      <c r="AV25" s="26">
+        <v>1534025</v>
+      </c>
+      <c r="AW25" s="23">
+        <v>45.587667161961363</v>
+      </c>
+      <c r="AX25" s="33">
+        <v>211000</v>
+      </c>
+      <c r="AY25" s="26">
+        <v>211000</v>
+      </c>
+      <c r="AZ25" s="26">
+        <v>906900</v>
+      </c>
+      <c r="BA25" s="55">
+        <v>42.981042654028428</v>
+      </c>
+      <c r="BB25" s="59">
+        <v>337.6</v>
+      </c>
+      <c r="BC25" s="78">
+        <v>314.3</v>
+      </c>
+      <c r="BD25" s="68">
+        <v>404</v>
+      </c>
+      <c r="BE25" s="55">
+        <v>463</v>
+      </c>
+      <c r="BF25" s="73">
+        <v>1450</v>
+      </c>
+      <c r="BG25" s="32">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="26" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A26" s="45" t="s">
+        <v>407</v>
+      </c>
+      <c r="B26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="N26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="O26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="P26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Z26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AA26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AB26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AC26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AG26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AI26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AK26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AL26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AX26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AY26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AZ26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BA26" s="55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BB26" s="59" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BC26" s="78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BD26" s="68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BE26" s="55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BF26" s="73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BG26" s="32" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -7559,7 +7744,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:BG25"/>
+  <dimension ref="A1:BG26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="54" width="11.42578125" style="3"/>
@@ -11176,178 +11361,357 @@
       <c r="A25" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="O25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="S25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="W25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="X25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AG25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AH25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AI25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AJ25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AK25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AL25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AM25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AO25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AR25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AS25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AT25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AX25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AY25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AZ25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="BA25" s="55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="BB25" s="59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="BC25" s="78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="BD25" s="68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="BE25" s="55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="BF25" s="73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="BG25" s="32" t="e">
+      <c r="B25" s="33">
+        <v>184000</v>
+      </c>
+      <c r="C25" s="26">
+        <v>140400</v>
+      </c>
+      <c r="D25" s="26">
+        <v>1241795</v>
+      </c>
+      <c r="E25" s="23">
+        <v>88.446937321937327</v>
+      </c>
+      <c r="F25" s="33">
+        <v>5250</v>
+      </c>
+      <c r="G25" s="26">
+        <v>3150</v>
+      </c>
+      <c r="H25" s="26">
+        <v>18540</v>
+      </c>
+      <c r="I25" s="23">
+        <v>58.857142857142861</v>
+      </c>
+      <c r="J25" s="33">
+        <v>1950</v>
+      </c>
+      <c r="K25" s="26">
+        <v>1100</v>
+      </c>
+      <c r="L25" s="26">
+        <v>7010</v>
+      </c>
+      <c r="M25" s="23">
+        <v>63.727272727272734</v>
+      </c>
+      <c r="N25" s="33">
+        <v>7800</v>
+      </c>
+      <c r="O25" s="26">
+        <v>5600</v>
+      </c>
+      <c r="P25" s="26">
+        <v>36910</v>
+      </c>
+      <c r="Q25" s="23">
+        <v>65.910714285714278</v>
+      </c>
+      <c r="R25" s="33">
+        <v>14750</v>
+      </c>
+      <c r="S25" s="26">
+        <v>10400</v>
+      </c>
+      <c r="T25" s="26">
+        <v>70060</v>
+      </c>
+      <c r="U25" s="23">
+        <v>67.365384615384613</v>
+      </c>
+      <c r="V25" s="33">
+        <v>12500</v>
+      </c>
+      <c r="W25" s="26">
+        <v>9100</v>
+      </c>
+      <c r="X25" s="26">
+        <v>66080</v>
+      </c>
+      <c r="Y25" s="23">
+        <v>72.615384615384613</v>
+      </c>
+      <c r="Z25" s="33">
+        <v>1450</v>
+      </c>
+      <c r="AA25" s="26">
+        <v>1150</v>
+      </c>
+      <c r="AB25" s="26">
+        <v>7320</v>
+      </c>
+      <c r="AC25" s="23">
+        <v>63.652173913043477</v>
+      </c>
+      <c r="AD25" s="33">
+        <v>150</v>
+      </c>
+      <c r="AE25" s="26">
+        <v>150</v>
+      </c>
+      <c r="AF25" s="26">
+        <v>855</v>
+      </c>
+      <c r="AG25" s="23">
+        <v>57</v>
+      </c>
+      <c r="AH25" s="33">
+        <v>40100</v>
+      </c>
+      <c r="AI25" s="26">
+        <v>31700</v>
+      </c>
+      <c r="AJ25" s="26">
+        <v>279160</v>
+      </c>
+      <c r="AK25" s="23">
+        <v>88.063091482649853</v>
+      </c>
+      <c r="AL25" s="33">
+        <v>20000</v>
+      </c>
+      <c r="AM25" s="26">
+        <v>14300</v>
+      </c>
+      <c r="AN25" s="26">
+        <v>125900</v>
+      </c>
+      <c r="AO25" s="23">
+        <v>88.041958041958054</v>
+      </c>
+      <c r="AP25" s="33">
+        <v>6150</v>
+      </c>
+      <c r="AQ25" s="26">
+        <v>4600</v>
+      </c>
+      <c r="AR25" s="26">
+        <v>39440</v>
+      </c>
+      <c r="AS25" s="23">
+        <v>85.739130434782595</v>
+      </c>
+      <c r="AT25" s="33">
+        <v>47600</v>
+      </c>
+      <c r="AU25" s="26">
+        <v>39050</v>
+      </c>
+      <c r="AV25" s="26">
+        <v>393460</v>
+      </c>
+      <c r="AW25" s="23">
+        <v>100.75800256081946</v>
+      </c>
+      <c r="AX25" s="33">
+        <v>26300</v>
+      </c>
+      <c r="AY25" s="26">
+        <v>20100</v>
+      </c>
+      <c r="AZ25" s="26">
+        <v>197060</v>
+      </c>
+      <c r="BA25" s="55">
+        <v>98.039800995024876</v>
+      </c>
+      <c r="BB25" s="59">
+        <v>178.04</v>
+      </c>
+      <c r="BC25" s="78">
+        <v>173.9</v>
+      </c>
+      <c r="BD25" s="59">
+        <v>197.4</v>
+      </c>
+      <c r="BE25" s="55">
+        <v>212.7</v>
+      </c>
+      <c r="BF25" s="73">
+        <v>1375</v>
+      </c>
+      <c r="BG25" s="32">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="26" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A26" s="45" t="s">
+        <v>407</v>
+      </c>
+      <c r="B26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="N26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="O26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="P26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Z26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AA26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AB26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AC26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AG26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AI26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AK26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AL26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AX26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AY26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AZ26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BA26" s="55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BB26" s="59" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BC26" s="78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BD26" s="68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BE26" s="55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BF26" s="73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BG26" s="32" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -11363,7 +11727,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:BG25"/>
+  <dimension ref="A1:BG26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="57" width="11.42578125" style="3"/>
@@ -15026,161 +15390,162 @@
       <c r="A25" s="45" t="s">
         <v>386</v>
       </c>
-      <c r="B25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="O25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="S25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="W25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="X25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AG25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AH25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AI25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AJ25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AK25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AL25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AM25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AO25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AR25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AS25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AT25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AX25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AY25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AZ25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="BA25" s="55" t="e">
-        <v>#N/A</v>
+      <c r="B25" s="33">
+        <v>476500</v>
+      </c>
+      <c r="C25" s="26">
+        <v>476100</v>
+      </c>
+      <c r="D25" s="26">
+        <v>2095035</v>
+      </c>
+      <c r="E25" s="23">
+        <f>D25/C25*10</f>
+        <v>44.004095778197858</v>
+      </c>
+      <c r="F25" s="33">
+        <v>30500</v>
+      </c>
+      <c r="G25" s="26">
+        <v>30300</v>
+      </c>
+      <c r="H25" s="26">
+        <v>98475</v>
+      </c>
+      <c r="I25" s="23">
+        <v>32.5</v>
+      </c>
+      <c r="J25" s="33">
+        <v>7850</v>
+      </c>
+      <c r="K25" s="26">
+        <v>7850</v>
+      </c>
+      <c r="L25" s="26">
+        <v>26690</v>
+      </c>
+      <c r="M25" s="23">
+        <v>34</v>
+      </c>
+      <c r="N25" s="33">
+        <v>29100</v>
+      </c>
+      <c r="O25" s="26">
+        <v>29100</v>
+      </c>
+      <c r="P25" s="26">
+        <v>103305</v>
+      </c>
+      <c r="Q25" s="23">
+        <v>35.5</v>
+      </c>
+      <c r="R25" s="33">
+        <v>32750</v>
+      </c>
+      <c r="S25" s="26">
+        <v>32750</v>
+      </c>
+      <c r="T25" s="26">
+        <v>131000</v>
+      </c>
+      <c r="U25" s="23">
+        <v>40</v>
+      </c>
+      <c r="V25" s="33">
+        <v>37500</v>
+      </c>
+      <c r="W25" s="26">
+        <v>37500</v>
+      </c>
+      <c r="X25" s="26">
+        <v>153750</v>
+      </c>
+      <c r="Y25" s="23">
+        <v>41</v>
+      </c>
+      <c r="Z25" s="33">
+        <v>6400</v>
+      </c>
+      <c r="AA25" s="26">
+        <v>6400</v>
+      </c>
+      <c r="AB25" s="26">
+        <v>23680</v>
+      </c>
+      <c r="AC25" s="23">
+        <v>37</v>
+      </c>
+      <c r="AD25" s="33">
+        <v>400</v>
+      </c>
+      <c r="AE25" s="26">
+        <v>400</v>
+      </c>
+      <c r="AF25" s="26">
+        <v>1360</v>
+      </c>
+      <c r="AG25" s="23">
+        <v>34</v>
+      </c>
+      <c r="AH25" s="33">
+        <v>92500</v>
+      </c>
+      <c r="AI25" s="26">
+        <v>92400</v>
+      </c>
+      <c r="AJ25" s="26">
+        <v>383460</v>
+      </c>
+      <c r="AK25" s="23">
+        <v>41.5</v>
+      </c>
+      <c r="AL25" s="33">
+        <v>55100</v>
+      </c>
+      <c r="AM25" s="26">
+        <v>55050</v>
+      </c>
+      <c r="AN25" s="26">
+        <v>225705</v>
+      </c>
+      <c r="AO25" s="23">
+        <v>41</v>
+      </c>
+      <c r="AP25" s="33">
+        <v>10200</v>
+      </c>
+      <c r="AQ25" s="26">
+        <v>10150</v>
+      </c>
+      <c r="AR25" s="26">
+        <v>40600</v>
+      </c>
+      <c r="AS25" s="23">
+        <v>40</v>
+      </c>
+      <c r="AT25" s="33">
+        <v>98800</v>
+      </c>
+      <c r="AU25" s="26">
+        <v>98800</v>
+      </c>
+      <c r="AV25" s="26">
+        <v>518700</v>
+      </c>
+      <c r="AW25" s="23">
+        <v>52.5</v>
+      </c>
+      <c r="AX25" s="33">
+        <v>75400</v>
+      </c>
+      <c r="AY25" s="26">
+        <v>75400</v>
+      </c>
+      <c r="AZ25" s="26">
+        <v>388310</v>
+      </c>
+      <c r="BA25" s="55">
+        <v>51.5</v>
       </c>
       <c r="BB25" s="59" t="e">
         <v>#N/A</v>
@@ -15194,10 +15559,189 @@
       <c r="BE25" s="55" t="e">
         <v>#N/A</v>
       </c>
-      <c r="BF25" s="73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="BG25" s="32" t="e">
+      <c r="BF25" s="73">
+        <v>1185</v>
+      </c>
+      <c r="BG25" s="32">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="26" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A26" s="45" t="s">
+        <v>408</v>
+      </c>
+      <c r="B26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="N26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="O26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="P26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Z26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AA26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AB26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AC26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AG26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AI26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AK26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AL26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AX26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AY26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AZ26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BA26" s="55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BB26" s="59" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BC26" s="78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BD26" s="68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BE26" s="55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BF26" s="73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BG26" s="32" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -15209,7 +15753,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A10:A25" numberStoredAsText="1"/>
+    <ignoredError sqref="A10:A26" numberStoredAsText="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
@@ -18696,172 +19240,346 @@
       <c r="A25" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="O25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="S25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="W25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="X25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AG25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AH25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AI25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AJ25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AK25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AL25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AM25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AO25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AR25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AS25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AT25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AX25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AY25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AZ25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="BA25" s="55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="BB25" s="56" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="BC25" s="79" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="BD25" s="69" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="BE25" s="32" t="e">
+      <c r="B25" s="33">
+        <v>160000</v>
+      </c>
+      <c r="C25" s="26">
+        <v>159500</v>
+      </c>
+      <c r="D25" s="26">
+        <v>382722.5</v>
+      </c>
+      <c r="E25" s="23">
+        <f>D25/C25*10</f>
+        <v>23.995141065830722</v>
+      </c>
+      <c r="F25" s="33">
+        <v>21000</v>
+      </c>
+      <c r="G25" s="26">
+        <v>20950</v>
+      </c>
+      <c r="H25" s="26">
+        <v>39805</v>
+      </c>
+      <c r="I25" s="23">
+        <v>19</v>
+      </c>
+      <c r="J25" s="33">
+        <v>7100</v>
+      </c>
+      <c r="K25" s="26">
+        <v>7050</v>
+      </c>
+      <c r="L25" s="26">
+        <v>14805</v>
+      </c>
+      <c r="M25" s="23">
+        <v>21</v>
+      </c>
+      <c r="N25" s="33">
+        <v>45500</v>
+      </c>
+      <c r="O25" s="26">
+        <v>45450</v>
+      </c>
+      <c r="P25" s="26">
+        <v>109080</v>
+      </c>
+      <c r="Q25" s="23">
+        <v>24</v>
+      </c>
+      <c r="R25" s="33">
+        <v>22500</v>
+      </c>
+      <c r="S25" s="26">
+        <v>22400</v>
+      </c>
+      <c r="T25" s="26">
+        <v>51520</v>
+      </c>
+      <c r="U25" s="23">
+        <v>23</v>
+      </c>
+      <c r="V25" s="33">
+        <v>20500</v>
+      </c>
+      <c r="W25" s="26">
+        <v>20450</v>
+      </c>
+      <c r="X25" s="26">
+        <v>51125</v>
+      </c>
+      <c r="Y25" s="23">
+        <v>25</v>
+      </c>
+      <c r="Z25" s="33">
+        <v>3700</v>
+      </c>
+      <c r="AA25" s="26">
+        <v>3650</v>
+      </c>
+      <c r="AB25" s="26">
+        <v>8030</v>
+      </c>
+      <c r="AC25" s="23">
+        <v>22</v>
+      </c>
+      <c r="AD25" s="33">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="26">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="26">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="23">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="33">
+        <v>20100</v>
+      </c>
+      <c r="AI25" s="26">
+        <v>20050</v>
+      </c>
+      <c r="AJ25" s="26">
+        <v>56140</v>
+      </c>
+      <c r="AK25" s="23">
+        <v>28</v>
+      </c>
+      <c r="AL25" s="33">
+        <v>11400</v>
+      </c>
+      <c r="AM25" s="26">
+        <v>11350</v>
+      </c>
+      <c r="AN25" s="26">
+        <v>30645</v>
+      </c>
+      <c r="AO25" s="23">
+        <v>27</v>
+      </c>
+      <c r="AP25" s="33">
+        <v>3500</v>
+      </c>
+      <c r="AQ25" s="26">
+        <v>3450</v>
+      </c>
+      <c r="AR25" s="26">
+        <v>9142.5</v>
+      </c>
+      <c r="AS25" s="23">
+        <v>26.5</v>
+      </c>
+      <c r="AT25" s="33">
+        <v>2600</v>
+      </c>
+      <c r="AU25" s="26">
+        <v>2600</v>
+      </c>
+      <c r="AV25" s="26">
+        <v>6760</v>
+      </c>
+      <c r="AW25" s="23">
+        <v>26</v>
+      </c>
+      <c r="AX25" s="33">
+        <v>2100</v>
+      </c>
+      <c r="AY25" s="26">
+        <v>2100</v>
+      </c>
+      <c r="AZ25" s="26">
+        <v>5670</v>
+      </c>
+      <c r="BA25" s="55">
+        <v>27</v>
+      </c>
+      <c r="BB25" s="59">
+        <v>337.31</v>
+      </c>
+      <c r="BC25" s="78">
+        <v>342.51</v>
+      </c>
+      <c r="BD25" s="69">
+        <v>1355</v>
+      </c>
+      <c r="BE25" s="32">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="26" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="A26" s="45" t="s">
+        <v>407</v>
+      </c>
+      <c r="B26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="N26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="O26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="P26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Z26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AA26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AB26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AC26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AG26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AI26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AK26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AL26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AX26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AY26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AZ26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BA26" s="55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BB26" s="56" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BC26" s="79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BD26" s="69" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BE26" s="32" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -18880,7 +19598,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:BG25"/>
+  <dimension ref="A1:BG26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="57" width="11.42578125" style="3"/>
@@ -22464,174 +23182,349 @@
       <c r="A25" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="O25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="S25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="W25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="X25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AF25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AG25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AH25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AI25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AJ25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AK25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AL25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AM25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AN25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AO25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AP25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AQ25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AR25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AS25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AT25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AU25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AV25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AW25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AX25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AY25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AZ25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="BA25" s="55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="BB25" s="56" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="BC25" s="79" t="e">
-        <v>#N/A</v>
+      <c r="B25" s="33">
+        <v>122300</v>
+      </c>
+      <c r="C25" s="26">
+        <v>67150</v>
+      </c>
+      <c r="D25" s="26">
+        <v>285370</v>
+      </c>
+      <c r="E25" s="23">
+        <v>42.5</v>
+      </c>
+      <c r="F25" s="33">
+        <v>28500</v>
+      </c>
+      <c r="G25" s="26">
+        <v>13500</v>
+      </c>
+      <c r="H25" s="26">
+        <v>39150</v>
+      </c>
+      <c r="I25" s="23">
+        <v>29</v>
+      </c>
+      <c r="J25" s="33">
+        <v>3200</v>
+      </c>
+      <c r="K25" s="26">
+        <v>1800</v>
+      </c>
+      <c r="L25" s="26">
+        <v>8640</v>
+      </c>
+      <c r="M25" s="23">
+        <v>48</v>
+      </c>
+      <c r="N25" s="33">
+        <v>6500</v>
+      </c>
+      <c r="O25" s="26">
+        <v>3600</v>
+      </c>
+      <c r="P25" s="26">
+        <v>8640</v>
+      </c>
+      <c r="Q25" s="23">
+        <v>24</v>
+      </c>
+      <c r="R25" s="33">
+        <v>30700</v>
+      </c>
+      <c r="S25" s="26">
+        <v>15000</v>
+      </c>
+      <c r="T25" s="26">
+        <v>67500</v>
+      </c>
+      <c r="U25" s="23">
+        <v>45</v>
+      </c>
+      <c r="V25" s="33">
+        <v>16500</v>
+      </c>
+      <c r="W25" s="26">
+        <v>10000</v>
+      </c>
+      <c r="X25" s="26">
+        <v>48000</v>
+      </c>
+      <c r="Y25" s="23">
+        <v>48</v>
+      </c>
+      <c r="Z25" s="33">
+        <v>1000</v>
+      </c>
+      <c r="AA25" s="26">
+        <v>500</v>
+      </c>
+      <c r="AB25" s="26">
+        <v>1750</v>
+      </c>
+      <c r="AC25" s="23">
+        <v>35</v>
+      </c>
+      <c r="AD25" s="33">
+        <v>300</v>
+      </c>
+      <c r="AE25" s="26">
+        <v>150</v>
+      </c>
+      <c r="AF25" s="26">
+        <v>630</v>
+      </c>
+      <c r="AG25" s="23">
+        <v>42</v>
+      </c>
+      <c r="AH25" s="33">
+        <v>15800</v>
+      </c>
+      <c r="AI25" s="26">
+        <v>7800</v>
+      </c>
+      <c r="AJ25" s="26">
+        <v>40560</v>
+      </c>
+      <c r="AK25" s="23">
+        <v>52</v>
+      </c>
+      <c r="AL25" s="33">
+        <v>8500</v>
+      </c>
+      <c r="AM25" s="26">
+        <v>4400</v>
+      </c>
+      <c r="AN25" s="26">
+        <v>22880</v>
+      </c>
+      <c r="AO25" s="23">
+        <v>52</v>
+      </c>
+      <c r="AP25" s="33">
+        <v>1100</v>
+      </c>
+      <c r="AQ25" s="26">
+        <v>700</v>
+      </c>
+      <c r="AR25" s="26">
+        <v>3290</v>
+      </c>
+      <c r="AS25" s="23">
+        <v>47</v>
+      </c>
+      <c r="AT25" s="33">
+        <v>7100</v>
+      </c>
+      <c r="AU25" s="26">
+        <v>6800</v>
+      </c>
+      <c r="AV25" s="26">
+        <v>31280</v>
+      </c>
+      <c r="AW25" s="23">
+        <v>46</v>
+      </c>
+      <c r="AX25" s="33">
+        <v>3100</v>
+      </c>
+      <c r="AY25" s="26">
+        <v>2900</v>
+      </c>
+      <c r="AZ25" s="26">
+        <v>13050</v>
+      </c>
+      <c r="BA25" s="55">
+        <v>45</v>
+      </c>
+      <c r="BB25" s="59">
+        <v>158.69999999999999</v>
+      </c>
+      <c r="BC25" s="78">
+        <v>189.2</v>
       </c>
       <c r="BD25" s="146"/>
       <c r="BE25" s="147"/>
-      <c r="BF25" s="74" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="BG25" s="32" t="e">
+      <c r="BF25" s="74">
+        <v>1450</v>
+      </c>
+      <c r="BG25" s="32">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="26" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="A26" s="45" t="s">
+        <v>407</v>
+      </c>
+      <c r="B26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="N26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="O26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="P26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Z26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AA26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AB26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AC26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AF26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AG26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AH26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AI26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AJ26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AK26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AL26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AM26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AN26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AO26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AP26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AQ26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AR26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AS26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AT26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AU26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AV26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AW26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AX26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AY26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AZ26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BA26" s="55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BB26" s="56" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BC26" s="79" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BD26" s="146"/>
+      <c r="BE26" s="147"/>
+      <c r="BF26" s="74" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="BG26" s="32" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -22647,7 +23540,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:BG25"/>
+  <dimension ref="A1:BG26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="29" width="11.42578125" style="3"/>
@@ -24646,94 +25539,189 @@
       <c r="A25" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="O25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="S25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="T25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="U25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="V25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="W25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="X25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Y25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Z25" s="59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AA25" s="78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AB25" s="68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AC25" s="55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AD25" s="73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="AE25" s="32" t="e">
+      <c r="B25" s="33">
+        <v>83700</v>
+      </c>
+      <c r="C25" s="26">
+        <v>76100</v>
+      </c>
+      <c r="D25" s="26">
+        <v>129405</v>
+      </c>
+      <c r="E25" s="23">
+        <v>1700</v>
+      </c>
+      <c r="F25" s="33">
+        <v>63600</v>
+      </c>
+      <c r="G25" s="26">
+        <v>58000</v>
+      </c>
+      <c r="H25" s="26">
+        <v>101500</v>
+      </c>
+      <c r="I25" s="23">
+        <v>1750</v>
+      </c>
+      <c r="J25" s="33">
+        <v>6850</v>
+      </c>
+      <c r="K25" s="26">
+        <v>4850</v>
+      </c>
+      <c r="L25" s="26">
+        <v>7760</v>
+      </c>
+      <c r="M25" s="23">
+        <v>1600</v>
+      </c>
+      <c r="N25" s="33">
+        <v>11450</v>
+      </c>
+      <c r="O25" s="26">
+        <v>11450</v>
+      </c>
+      <c r="P25" s="26">
+        <v>17175</v>
+      </c>
+      <c r="Q25" s="23">
+        <v>1500</v>
+      </c>
+      <c r="R25" s="33">
+        <v>0</v>
+      </c>
+      <c r="S25" s="26">
+        <v>0</v>
+      </c>
+      <c r="T25" s="26">
+        <v>0</v>
+      </c>
+      <c r="U25" s="23">
+        <v>0</v>
+      </c>
+      <c r="V25" s="33">
+        <v>1800</v>
+      </c>
+      <c r="W25" s="26">
+        <v>1800</v>
+      </c>
+      <c r="X25" s="26">
+        <v>2970</v>
+      </c>
+      <c r="Y25" s="23">
+        <v>1650</v>
+      </c>
+      <c r="Z25" s="59">
+        <v>1.24</v>
+      </c>
+      <c r="AA25" s="78">
+        <v>1.32</v>
+      </c>
+      <c r="AB25" s="68">
+        <v>1.66</v>
+      </c>
+      <c r="AC25" s="55">
+        <v>1.7</v>
+      </c>
+      <c r="AD25" s="73">
+        <v>1462</v>
+      </c>
+      <c r="AE25" s="32">
+        <v>1396.34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A26" s="45" t="s">
+        <v>407</v>
+      </c>
+      <c r="B26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="N26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="O26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="P26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="T26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="U26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="V26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="W26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="X26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Y26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Z26" s="59" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AA26" s="78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AB26" s="68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AC26" s="55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AD26" s="73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="AE26" s="32" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -24749,7 +25737,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:S25"/>
+  <dimension ref="A1:S26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="13" width="11.42578125" style="3"/>
@@ -25993,58 +26981,117 @@
       <c r="A25" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="C25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="D25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="E25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="F25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="G25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="H25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="I25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="J25" s="33" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="K25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="L25" s="26" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="M25" s="23" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="N25" s="59" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="O25" s="78" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="P25" s="68" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="Q25" s="55" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="R25" s="73" t="e">
-        <v>#N/A</v>
-      </c>
-      <c r="S25" s="32" t="e">
+      <c r="B25" s="33">
+        <v>31150</v>
+      </c>
+      <c r="C25" s="26">
+        <v>31150</v>
+      </c>
+      <c r="D25" s="26">
+        <v>182015</v>
+      </c>
+      <c r="E25" s="23">
+        <v>58.43</v>
+      </c>
+      <c r="F25" s="33">
+        <v>16000</v>
+      </c>
+      <c r="G25" s="26">
+        <v>16000</v>
+      </c>
+      <c r="H25" s="26">
+        <v>89600</v>
+      </c>
+      <c r="I25" s="23">
+        <v>56</v>
+      </c>
+      <c r="J25" s="33">
+        <v>15150</v>
+      </c>
+      <c r="K25" s="26">
+        <v>15150</v>
+      </c>
+      <c r="L25" s="26">
+        <v>92415</v>
+      </c>
+      <c r="M25" s="23">
+        <v>61</v>
+      </c>
+      <c r="N25" s="59">
+        <v>22500</v>
+      </c>
+      <c r="O25" s="78">
+        <v>25000</v>
+      </c>
+      <c r="P25" s="68">
+        <v>371.5</v>
+      </c>
+      <c r="Q25" s="55">
+        <v>345.8</v>
+      </c>
+      <c r="R25" s="73">
+        <v>1375</v>
+      </c>
+      <c r="S25" s="32">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A26" s="45" t="s">
+        <v>407</v>
+      </c>
+      <c r="B26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="C26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="D26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="E26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="F26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="G26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="H26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="I26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="J26" s="33" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="K26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="L26" s="26" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="M26" s="23" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="N26" s="59" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="O26" s="78" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="P26" s="68" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="Q26" s="55" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="R26" s="73" t="e">
+        <v>#N/A</v>
+      </c>
+      <c r="S26" s="32" t="e">
         <v>#N/A</v>
       </c>
     </row>
@@ -26058,6 +27105,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5dd4176-d247-4204-85b8-921214f3ccea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="359b39ce-e1f9-4933-8424-33b611e6fdcd" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -26066,7 +27124,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100C5B9F2161CEE1040BBC03CB11300495F" ma:contentTypeVersion="12" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="a7cec21613a3259523bdab11a1e26aca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b5dd4176-d247-4204-85b8-921214f3ccea" xmlns:ns3="359b39ce-e1f9-4933-8424-33b611e6fdcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="68943c349d3a016936c8f8cb3335004b" ns2:_="" ns3:_="">
     <xsd:import namespace="b5dd4176-d247-4204-85b8-921214f3ccea"/>
@@ -26267,30 +27325,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="b5dd4176-d247-4204-85b8-921214f3ccea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="359b39ce-e1f9-4933-8424-33b611e6fdcd" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73388873-A235-4C5D-B547-49D87C813EAC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1895075E-5D11-4C60-B094-C6D3F8016EBC}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F626F8A7-ADA2-4AE2-ACFA-07C6B901584A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -26299,4 +27334,31 @@
     <ds:schemaRef ds:uri="359b39ce-e1f9-4933-8424-33b611e6fdcd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73388873-A235-4C5D-B547-49D87C813EAC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1895075E-5D11-4C60-B094-C6D3F8016EBC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b5dd4176-d247-4204-85b8-921214f3ccea"/>
+    <ds:schemaRef ds:uri="359b39ce-e1f9-4933-8424-33b611e6fdcd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>